--- a/预测经验跟踪.xlsx
+++ b/预测经验跟踪.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,9 @@
     <font>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -82,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -101,6 +104,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -467,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -533,6 +542,11 @@
           <t>经验与失败原因（必读）</t>
         </is>
       </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>收盘前预测下一交易日</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="62" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -791,6 +805,65 @@
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>待验证（10-22 收盘后回填）。本版起区间按新规收窄至宽度 ≤1%（10-21 22:50 修订，原宽区间版作废）；关注宁德时代杀跌延续性、南向能否回流、今夜特斯拉/Meta 财报对 AI 资本开支的压力测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>中性偏强、震荡整固 3680~3712</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>分化、反弹与兑现并存 2672~2698</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>中性偏弱、平开震荡 22950~23150</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>高开尝试修复、冲高易回落 3845~3882</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>收盘前(14:30)新增“收盘前预测下一交易日”列，预测见K列。</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>下一开盘日 2026-10-27（收盘前预测）：
+上证：平开至小幅低开 3675~3695；收盘中性偏谨慎 3672~3708；全天 3662~3715；中低置信。变量：美联储议息、3670承接、3700得失。
+恒科：平开至小幅低开 3835~3875；收盘中性偏弱 3824~3862；全天 3810~3865；中低置信。变量：南向净卖出、腾讯/小米、3900压力、美联储议息。</t>
         </is>
       </c>
     </row>
